--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
@@ -517,13 +517,10 @@
         <v>28.6</v>
       </c>
       <c r="E2">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>24.1</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="H2">
         <v>20.2</v>
@@ -572,18 +569,12 @@
       <c r="F3">
         <v>25.4</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
         <v>18.9</v>
       </c>
       <c r="I3">
         <v>32.6</v>
       </c>
-      <c r="J3">
-        <v>27.2</v>
-      </c>
       <c r="K3">
         <v>18.8</v>
       </c>
@@ -622,9 +613,6 @@
       <c r="F4">
         <v>26.5</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
         <v>20</v>
       </c>
@@ -660,33 +648,21 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>34.8</v>
-      </c>
       <c r="E5">
         <v>19.3</v>
       </c>
-      <c r="F5">
-        <v>27</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>20.1</v>
-      </c>
       <c r="I5">
         <v>34.2</v>
       </c>
-      <c r="J5">
-        <v>29.5</v>
-      </c>
-      <c r="K5">
-        <v>20.1</v>
-      </c>
       <c r="M5">
         <v>24.4</v>
       </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5" t="s">
+        <v>20</v>
+      </c>
       <c r="R5" s="2">
         <v>25327</v>
       </c>
@@ -716,9 +692,6 @@
       <c r="F6">
         <v>27.6</v>
       </c>
-      <c r="G6">
-        <v>30.9</v>
-      </c>
       <c r="H6">
         <v>21</v>
       </c>
@@ -758,20 +731,23 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="E7">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="F7">
         <v>24.9</v>
       </c>
-      <c r="H7">
-        <v>21.2</v>
+      <c r="G7">
+        <v>0</v>
       </c>
       <c r="I7">
         <v>29.9</v>
       </c>
+      <c r="J7">
+        <v>27.1</v>
+      </c>
       <c r="K7">
         <v>20.9</v>
       </c>
@@ -807,12 +783,27 @@
       <c r="F8">
         <v>27.2</v>
       </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
       <c r="H8">
         <v>23.3</v>
       </c>
+      <c r="I8">
+        <v>31.8</v>
+      </c>
+      <c r="J8">
+        <v>27.9</v>
+      </c>
       <c r="K8">
         <v>23</v>
       </c>
+      <c r="L8">
+        <v>24.9</v>
+      </c>
+      <c r="M8">
+        <v>23.4</v>
+      </c>
       <c r="R8" s="2">
         <v>25330</v>
       </c>
@@ -837,17 +828,23 @@
         <v>32.8</v>
       </c>
       <c r="E9">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="F9">
         <v>26.6</v>
       </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
       <c r="H9">
         <v>22.1</v>
       </c>
       <c r="I9">
         <v>32.6</v>
       </c>
+      <c r="J9">
+        <v>28</v>
+      </c>
       <c r="K9">
         <v>21.9</v>
       </c>
@@ -883,12 +880,27 @@
       <c r="F10">
         <v>26.3</v>
       </c>
+      <c r="G10">
+        <v>11.1</v>
+      </c>
       <c r="H10">
         <v>22.4</v>
       </c>
+      <c r="I10">
+        <v>22.4</v>
+      </c>
+      <c r="J10">
+        <v>22</v>
+      </c>
       <c r="K10">
         <v>22.1</v>
       </c>
+      <c r="L10">
+        <v>21.1</v>
+      </c>
+      <c r="M10">
+        <v>21.6</v>
+      </c>
       <c r="R10" s="2">
         <v>25332</v>
       </c>
@@ -910,16 +922,19 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="E11">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="F11">
-        <v>26.6</v>
+        <v>26.7</v>
+      </c>
+      <c r="G11">
+        <v>25.7</v>
       </c>
       <c r="H11">
-        <v>21.6</v>
+        <v>24</v>
       </c>
       <c r="I11">
         <v>32</v>
@@ -928,7 +943,7 @@
         <v>28.7</v>
       </c>
       <c r="K11">
-        <v>21.6</v>
+        <v>24</v>
       </c>
       <c r="L11">
         <v>23.6</v>
@@ -963,20 +978,20 @@
         <v>21.2</v>
       </c>
       <c r="F12">
-        <v>26.6</v>
-      </c>
-      <c r="H12">
-        <v>21.4</v>
+        <v>26.7</v>
       </c>
       <c r="I12">
         <v>32.1</v>
       </c>
-      <c r="J12">
-        <v>28.5</v>
-      </c>
       <c r="K12">
         <v>21.1</v>
       </c>
+      <c r="L12">
+        <v>22.8</v>
+      </c>
+      <c r="M12">
+        <v>24.4</v>
+      </c>
       <c r="R12" s="2">
         <v>25334</v>
       </c>
@@ -1012,15 +1027,15 @@
       <c r="I13">
         <v>29.9</v>
       </c>
-      <c r="J13">
-        <v>24.3</v>
-      </c>
       <c r="K13">
         <v>22</v>
       </c>
       <c r="L13">
         <v>24.7</v>
       </c>
+      <c r="M13">
+        <v>22.9</v>
+      </c>
       <c r="R13" s="2">
         <v>25335</v>
       </c>
@@ -1041,26 +1056,26 @@
       <c r="C14">
         <v>13</v>
       </c>
+      <c r="D14">
+        <v>31.4</v>
+      </c>
       <c r="E14">
-        <v>18.5</v>
+        <v>21.5</v>
       </c>
       <c r="F14">
-        <v>28.5</v>
-      </c>
-      <c r="H14">
-        <v>21.6</v>
+        <v>26.5</v>
       </c>
       <c r="I14">
         <v>30.7</v>
       </c>
-      <c r="J14">
-        <v>27.3</v>
-      </c>
       <c r="K14">
         <v>21.4</v>
       </c>
-      <c r="N14" t="s">
-        <v>20</v>
+      <c r="L14">
+        <v>22.7</v>
+      </c>
+      <c r="M14">
+        <v>23.8</v>
       </c>
       <c r="R14" s="2">
         <v>25336</v>
@@ -1083,7 +1098,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="E15">
         <v>21.2</v>
@@ -1097,15 +1112,15 @@
       <c r="I15">
         <v>30.6</v>
       </c>
-      <c r="J15">
-        <v>27.8</v>
-      </c>
       <c r="K15">
         <v>21.5</v>
       </c>
       <c r="L15">
         <v>24.7</v>
       </c>
+      <c r="M15">
+        <v>24.6</v>
+      </c>
       <c r="R15" s="2">
         <v>25337</v>
       </c>
@@ -1135,18 +1150,18 @@
       <c r="F16">
         <v>27</v>
       </c>
-      <c r="H16">
-        <v>21.3</v>
-      </c>
       <c r="I16">
         <v>32.4</v>
       </c>
-      <c r="J16">
-        <v>26.5</v>
-      </c>
       <c r="K16">
         <v>21</v>
       </c>
+      <c r="L16">
+        <v>25.9</v>
+      </c>
+      <c r="M16">
+        <v>24.6</v>
+      </c>
       <c r="R16" s="2">
         <v>25338</v>
       </c>
@@ -1176,20 +1191,20 @@
       <c r="F17">
         <v>23.5</v>
       </c>
+      <c r="G17">
+        <v>23.7</v>
+      </c>
       <c r="H17">
         <v>22.4</v>
       </c>
-      <c r="I17">
-        <v>26.2</v>
-      </c>
-      <c r="K17">
-        <v>22.1</v>
+      <c r="J17">
+        <v>24.4</v>
       </c>
       <c r="L17">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="M17">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="R17" s="2">
         <v>25339</v>
@@ -1212,20 +1227,20 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>25.1</v>
+        <v>26.2</v>
       </c>
       <c r="E18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <v>23.1</v>
       </c>
+      <c r="G18">
+        <v>6.7</v>
+      </c>
       <c r="H18">
         <v>21.4</v>
       </c>
-      <c r="I18">
-        <v>24.3</v>
-      </c>
       <c r="J18">
         <v>23.8</v>
       </c>
@@ -1236,7 +1251,7 @@
         <v>23.3</v>
       </c>
       <c r="M18">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="R18" s="2">
         <v>25340</v>
@@ -1259,7 +1274,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="E19">
         <v>20.6</v>
@@ -1267,8 +1282,14 @@
       <c r="F19">
         <v>25.5</v>
       </c>
-      <c r="I19">
-        <v>28.8</v>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>20.7</v>
+      </c>
+      <c r="J19">
+        <v>26.9</v>
       </c>
       <c r="K19">
         <v>20.5</v>
@@ -1300,7 +1321,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="E20">
         <v>20.5</v>
@@ -1308,17 +1329,17 @@
       <c r="F20">
         <v>26.1</v>
       </c>
-      <c r="I20">
-        <v>31.2</v>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>20.9</v>
       </c>
       <c r="J20">
         <v>28.6</v>
       </c>
-      <c r="K20">
-        <v>20.6</v>
-      </c>
       <c r="L20">
-        <v>22.5</v>
+        <v>24.8</v>
       </c>
       <c r="M20">
         <v>23.2</v>
@@ -1352,11 +1373,14 @@
       <c r="F21">
         <v>26</v>
       </c>
-      <c r="I21">
-        <v>25.3</v>
-      </c>
-      <c r="K21">
-        <v>20.6</v>
+      <c r="G21">
+        <v>8.4</v>
+      </c>
+      <c r="H21">
+        <v>20.1</v>
+      </c>
+      <c r="J21">
+        <v>22.4</v>
       </c>
       <c r="L21">
         <v>23.6</v>
@@ -1387,23 +1411,32 @@
       <c r="D22">
         <v>31.1</v>
       </c>
+      <c r="E22">
+        <v>19.3</v>
+      </c>
       <c r="F22">
-        <v>23.2</v>
+        <v>25.2</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="I22">
         <v>31.1</v>
       </c>
+      <c r="J22">
+        <v>27.4</v>
+      </c>
       <c r="K22">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="L22">
         <v>22.7</v>
       </c>
-      <c r="O22" t="s">
-        <v>20</v>
+      <c r="M22">
+        <v>23.8</v>
       </c>
       <c r="R22" s="2">
         <v>25344</v>
@@ -1434,18 +1467,27 @@
       <c r="F23">
         <v>24.4</v>
       </c>
+      <c r="G23">
+        <v>4.8</v>
+      </c>
       <c r="H23">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="I23">
         <v>28.9</v>
       </c>
+      <c r="J23">
+        <v>25.6</v>
+      </c>
       <c r="K23">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="L23">
         <v>23.1</v>
       </c>
+      <c r="M23">
+        <v>23.8</v>
+      </c>
       <c r="R23" s="2">
         <v>25345</v>
       </c>
@@ -1470,10 +1512,13 @@
         <v>31.9</v>
       </c>
       <c r="E24">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="F24">
-        <v>26.6</v>
+        <v>26.7</v>
+      </c>
+      <c r="G24">
+        <v>0.2</v>
       </c>
       <c r="H24">
         <v>21.8</v>
@@ -1481,12 +1526,18 @@
       <c r="I24">
         <v>30.5</v>
       </c>
+      <c r="J24">
+        <v>27.3</v>
+      </c>
       <c r="K24">
         <v>21.7</v>
       </c>
       <c r="L24">
         <v>24.2</v>
       </c>
+      <c r="M24">
+        <v>24.8</v>
+      </c>
       <c r="R24" s="2">
         <v>25346</v>
       </c>
@@ -1511,20 +1562,32 @@
         <v>31.1</v>
       </c>
       <c r="E25">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F25">
         <v>25.9</v>
       </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
       <c r="H25">
         <v>21.6</v>
       </c>
       <c r="I25">
         <v>31.1</v>
       </c>
+      <c r="J25">
+        <v>27.8</v>
+      </c>
       <c r="K25">
         <v>21.3</v>
       </c>
+      <c r="L25">
+        <v>22.6</v>
+      </c>
+      <c r="M25">
+        <v>23.5</v>
+      </c>
       <c r="R25" s="2">
         <v>25347</v>
       </c>
@@ -1554,18 +1617,27 @@
       <c r="F26">
         <v>26.5</v>
       </c>
+      <c r="G26">
+        <v>30.6</v>
+      </c>
       <c r="H26">
         <v>21</v>
       </c>
       <c r="I26">
         <v>32.1</v>
       </c>
+      <c r="J26">
+        <v>28.7</v>
+      </c>
       <c r="K26">
         <v>20.7</v>
       </c>
       <c r="L26">
         <v>23.9</v>
       </c>
+      <c r="M26">
+        <v>24.6</v>
+      </c>
       <c r="R26" s="2">
         <v>25348</v>
       </c>
@@ -1598,6 +1670,9 @@
       <c r="H27">
         <v>21</v>
       </c>
+      <c r="I27">
+        <v>31.9</v>
+      </c>
       <c r="K27">
         <v>20.9</v>
       </c>
@@ -1628,7 +1703,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="E28">
         <v>18.8</v>
@@ -1642,6 +1717,9 @@
       <c r="I28">
         <v>32.8</v>
       </c>
+      <c r="J28">
+        <v>27.8</v>
+      </c>
       <c r="K28">
         <v>19.6</v>
       </c>
@@ -1649,7 +1727,7 @@
         <v>23.7</v>
       </c>
       <c r="M28">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="R28" s="2">
         <v>25350</v>
@@ -1683,6 +1761,9 @@
       <c r="H29">
         <v>19.9</v>
       </c>
+      <c r="I29">
+        <v>22.3</v>
+      </c>
       <c r="K29">
         <v>19.8</v>
       </c>
@@ -1727,11 +1808,14 @@
       <c r="I30">
         <v>24.1</v>
       </c>
+      <c r="K30">
+        <v>21.8</v>
+      </c>
       <c r="L30">
         <v>23.8</v>
       </c>
       <c r="M30">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="R30" s="2">
         <v>25352</v>
@@ -1754,25 +1838,28 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>28.1</v>
+        <v>30</v>
       </c>
       <c r="E31">
         <v>21.3</v>
       </c>
       <c r="F31">
-        <v>24.7</v>
+        <v>25.7</v>
       </c>
       <c r="H31">
         <v>21.6</v>
       </c>
-      <c r="J31">
-        <v>27.8</v>
+      <c r="I31">
+        <v>29.1</v>
+      </c>
+      <c r="K31">
+        <v>21.5</v>
       </c>
       <c r="L31">
         <v>25.5</v>
       </c>
       <c r="M31">
-        <v>23.6</v>
+        <v>24.7</v>
       </c>
       <c r="R31" s="2">
         <v>25353</v>
@@ -1839,7 +1926,7 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="E33">
         <v>22.7</v>
@@ -1847,9 +1934,6 @@
       <c r="F33">
         <v>28.1</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
       <c r="H33">
         <v>23</v>
       </c>
@@ -1866,7 +1950,7 @@
         <v>23</v>
       </c>
       <c r="M33">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="R33" s="2">
         <v>25355</v>
@@ -1897,9 +1981,6 @@
       <c r="F34">
         <v>25.9</v>
       </c>
-      <c r="G34">
-        <v>1.9</v>
-      </c>
       <c r="H34">
         <v>21.6</v>
       </c>
@@ -1909,14 +1990,11 @@
       <c r="J34">
         <v>22</v>
       </c>
-      <c r="K34">
-        <v>22.4</v>
-      </c>
       <c r="L34">
         <v>23</v>
       </c>
       <c r="M34">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="R34" s="2">
         <v>25356</v>
@@ -1947,9 +2025,6 @@
       <c r="F35">
         <v>26.3</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
       <c r="H35">
         <v>21.6</v>
       </c>
@@ -1963,10 +2038,10 @@
         <v>21.3</v>
       </c>
       <c r="L35">
-        <v>24.9</v>
+        <v>22.5</v>
       </c>
       <c r="M35">
-        <v>24.8</v>
+        <v>23.5</v>
       </c>
       <c r="R35" s="2">
         <v>25357</v>
@@ -1997,9 +2072,6 @@
       <c r="F36">
         <v>26.7</v>
       </c>
-      <c r="G36">
-        <v>0.1</v>
-      </c>
       <c r="H36">
         <v>21.1</v>
       </c>
@@ -2042,14 +2114,11 @@
         <v>33.3</v>
       </c>
       <c r="E37">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="F37">
         <v>27.5</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
       <c r="H37">
         <v>22.1</v>
       </c>
@@ -2063,10 +2132,10 @@
         <v>21.7</v>
       </c>
       <c r="L37">
-        <v>25.6</v>
+        <v>22.9</v>
       </c>
       <c r="M37">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="R37" s="2">
         <v>25359</v>
@@ -2097,6 +2166,9 @@
       <c r="F38">
         <v>26.6</v>
       </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
       <c r="H38">
         <v>20.6</v>
       </c>
@@ -2110,10 +2182,10 @@
         <v>20.5</v>
       </c>
       <c r="L38">
-        <v>25.8</v>
+        <v>23.2</v>
       </c>
       <c r="M38">
-        <v>25.1</v>
+        <v>23.5</v>
       </c>
       <c r="R38" s="2">
         <v>25360</v>
@@ -2144,6 +2216,9 @@
       <c r="F39">
         <v>26.5</v>
       </c>
+      <c r="G39">
+        <v>4.8</v>
+      </c>
       <c r="H39">
         <v>20.4</v>
       </c>
@@ -2159,9 +2234,6 @@
       <c r="L39">
         <v>23.4</v>
       </c>
-      <c r="M39">
-        <v>25.6</v>
-      </c>
       <c r="R39" s="2">
         <v>25361</v>
       </c>
@@ -2183,14 +2255,17 @@
         <v>8</v>
       </c>
       <c r="D40">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E40">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F40">
         <v>24.9</v>
       </c>
+      <c r="G40">
+        <v>11.6</v>
+      </c>
       <c r="H40">
         <v>21.3</v>
       </c>
@@ -2206,9 +2281,6 @@
       <c r="L40">
         <v>22.5</v>
       </c>
-      <c r="M40">
-        <v>22.8</v>
-      </c>
       <c r="R40" s="2">
         <v>25362</v>
       </c>
@@ -2230,13 +2302,16 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="E41">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="F41">
-        <v>23.6</v>
+        <v>23.5</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
       </c>
       <c r="H41">
         <v>21.1</v>
@@ -2253,9 +2328,6 @@
       <c r="L41">
         <v>23.1</v>
       </c>
-      <c r="M41">
-        <v>24</v>
-      </c>
       <c r="R41" s="2">
         <v>25363</v>
       </c>
@@ -2277,13 +2349,16 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E42">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="F42">
-        <v>25.4</v>
+        <v>25.3</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
       </c>
       <c r="H42">
         <v>19.5</v>
@@ -2324,7 +2399,7 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="E43">
         <v>19.2</v>
@@ -2345,13 +2420,13 @@
         <v>28.3</v>
       </c>
       <c r="K43">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="L43">
         <v>22.8</v>
       </c>
       <c r="M43">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="R43" s="2">
         <v>25365</v>
@@ -2385,12 +2460,18 @@
       <c r="G44">
         <v>4.2</v>
       </c>
+      <c r="H44">
+        <v>20.9</v>
+      </c>
       <c r="I44">
         <v>31.7</v>
       </c>
       <c r="J44">
         <v>25.7</v>
       </c>
+      <c r="K44">
+        <v>20.7</v>
+      </c>
       <c r="L44">
         <v>23.1</v>
       </c>
@@ -2439,7 +2520,7 @@
         <v>25</v>
       </c>
       <c r="K45">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="L45">
         <v>22.3</v>
@@ -2471,7 +2552,7 @@
         <v>30.1</v>
       </c>
       <c r="E46">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="F46">
         <v>24.1</v>
@@ -2479,17 +2560,23 @@
       <c r="G46">
         <v>0</v>
       </c>
+      <c r="H46">
+        <v>18.9</v>
+      </c>
       <c r="I46">
         <v>30.1</v>
       </c>
       <c r="J46">
         <v>26.3</v>
       </c>
+      <c r="K46">
+        <v>18.9</v>
+      </c>
       <c r="L46">
         <v>22.3</v>
       </c>
       <c r="M46">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="R46" s="2">
         <v>25368</v>
@@ -2526,6 +2613,9 @@
       <c r="H47">
         <v>19.1</v>
       </c>
+      <c r="I47">
+        <v>31</v>
+      </c>
       <c r="J47">
         <v>24</v>
       </c>
@@ -2536,7 +2626,7 @@
         <v>25.8</v>
       </c>
       <c r="M47">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="R47" s="2">
         <v>25369</v>
@@ -2559,20 +2649,29 @@
         <v>16</v>
       </c>
       <c r="D48">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="E48">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="F48">
         <v>24.9</v>
       </c>
+      <c r="G48">
+        <v>5.6</v>
+      </c>
+      <c r="I48">
+        <v>22.9</v>
+      </c>
       <c r="J48">
         <v>21.5</v>
       </c>
       <c r="L48">
         <v>22.1</v>
       </c>
+      <c r="M48">
+        <v>21</v>
+      </c>
       <c r="R48" s="2">
         <v>25370</v>
       </c>
@@ -2602,11 +2701,17 @@
       <c r="F49">
         <v>26.1</v>
       </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>31.4</v>
+      </c>
       <c r="J49">
         <v>27.2</v>
       </c>
       <c r="L49">
-        <v>24.1</v>
+        <v>21.3</v>
       </c>
       <c r="M49">
         <v>22.2</v>
@@ -2632,13 +2737,16 @@
         <v>18</v>
       </c>
       <c r="D50">
-        <v>37</v>
+        <v>32.9</v>
       </c>
       <c r="E50">
         <v>19.2</v>
       </c>
       <c r="F50">
-        <v>28.1</v>
+        <v>26</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
       </c>
       <c r="H50">
         <v>19.6</v>
@@ -2655,6 +2763,9 @@
       <c r="L50">
         <v>22</v>
       </c>
+      <c r="M50">
+        <v>25.5</v>
+      </c>
       <c r="R50" s="2">
         <v>25372</v>
       </c>
@@ -2676,13 +2787,16 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>33.8</v>
+        <v>32.6</v>
       </c>
       <c r="E51">
         <v>19.8</v>
       </c>
       <c r="F51">
-        <v>26.8</v>
+        <v>26.2</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
       </c>
       <c r="I51">
         <v>29.7</v>
@@ -2693,6 +2807,9 @@
       <c r="L51">
         <v>23.5</v>
       </c>
+      <c r="M51">
+        <v>22.6</v>
+      </c>
       <c r="R51" s="2">
         <v>25373</v>
       </c>
@@ -2714,17 +2831,23 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="E52">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F52">
-        <v>24.8</v>
+        <v>24.7</v>
+      </c>
+      <c r="G52">
+        <v>18.1</v>
       </c>
       <c r="H52">
         <v>21.9</v>
       </c>
+      <c r="I52">
+        <v>28.6</v>
+      </c>
       <c r="J52">
         <v>25</v>
       </c>
@@ -2732,10 +2855,10 @@
         <v>21.5</v>
       </c>
       <c r="L52">
-        <v>24.8</v>
+        <v>23.4</v>
       </c>
       <c r="M52">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="R52" s="2">
         <v>25374</v>
@@ -2782,7 +2905,7 @@
         <v>22.9</v>
       </c>
       <c r="M53">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
       <c r="R53" s="2">
         <v>25375</v>
@@ -2826,10 +2949,10 @@
         <v>20.6</v>
       </c>
       <c r="L54">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
       <c r="M54">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="R54" s="2">
         <v>25376</v>
@@ -2908,17 +3031,23 @@
         <v>24.1</v>
       </c>
       <c r="H56">
-        <v>19</v>
+        <v>11.9</v>
+      </c>
+      <c r="I56">
+        <v>28.3</v>
       </c>
       <c r="J56">
         <v>26.3</v>
       </c>
       <c r="K56">
-        <v>19.1</v>
+        <v>11.9</v>
       </c>
       <c r="L56">
         <v>24.8</v>
       </c>
+      <c r="M56">
+        <v>24.4</v>
+      </c>
       <c r="R56" s="2">
         <v>25378</v>
       </c>
@@ -2951,6 +3080,9 @@
       <c r="H57">
         <v>21.9</v>
       </c>
+      <c r="I57">
+        <v>21.5</v>
+      </c>
       <c r="J57">
         <v>21.4</v>
       </c>
@@ -2958,7 +3090,10 @@
         <v>21.7</v>
       </c>
       <c r="L57">
-        <v>20.9</v>
+        <v>20.6</v>
+      </c>
+      <c r="M57">
+        <v>20.8</v>
       </c>
       <c r="R57" s="2">
         <v>25379</v>
@@ -2999,13 +3134,13 @@
         <v>27.8</v>
       </c>
       <c r="K58">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="L58">
-        <v>23.7</v>
+        <v>25.5</v>
       </c>
       <c r="M58">
-        <v>22.5</v>
+        <v>23.9</v>
       </c>
       <c r="R58" s="2">
         <v>25380</v>
@@ -3031,7 +3166,7 @@
         <v>30.8</v>
       </c>
       <c r="E59">
-        <v>20.6</v>
+        <v>20.06</v>
       </c>
       <c r="F59">
         <v>25.7</v>
@@ -3046,10 +3181,10 @@
         <v>28</v>
       </c>
       <c r="K59">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="L59">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="M59">
         <v>24</v>
@@ -3086,6 +3221,9 @@
       <c r="H60">
         <v>20.9</v>
       </c>
+      <c r="I60">
+        <v>29.3</v>
+      </c>
       <c r="J60">
         <v>27.1</v>
       </c>
@@ -3136,6 +3274,9 @@
       <c r="J61">
         <v>27.1</v>
       </c>
+      <c r="K61">
+        <v>21.2</v>
+      </c>
       <c r="L61">
         <v>22.7</v>
       </c>
@@ -3174,6 +3315,9 @@
       <c r="H62">
         <v>21.2</v>
       </c>
+      <c r="I62">
+        <v>24.7</v>
+      </c>
       <c r="J62">
         <v>24</v>
       </c>
@@ -3181,7 +3325,7 @@
         <v>21.1</v>
       </c>
       <c r="L62">
-        <v>21.7</v>
+        <v>20.4</v>
       </c>
       <c r="M62">
         <v>22</v>

--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -514,13 +514,16 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="E2">
         <v>20</v>
       </c>
       <c r="F2">
-        <v>24.4</v>
+        <v>24.3</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
       <c r="H2">
         <v>20.2</v>
@@ -569,12 +572,18 @@
       <c r="F3">
         <v>25.4</v>
       </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
       <c r="H3">
         <v>18.9</v>
       </c>
       <c r="I3">
         <v>32.6</v>
       </c>
+      <c r="J3">
+        <v>27.2</v>
+      </c>
       <c r="K3">
         <v>18.8</v>
       </c>
@@ -613,6 +622,9 @@
       <c r="F4">
         <v>26.5</v>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
       <c r="H4">
         <v>20</v>
       </c>
@@ -625,6 +637,9 @@
       <c r="K4">
         <v>20</v>
       </c>
+      <c r="L4">
+        <v>25.7</v>
+      </c>
       <c r="M4">
         <v>21.8</v>
       </c>
@@ -648,21 +663,36 @@
       <c r="C5">
         <v>4</v>
       </c>
+      <c r="D5">
+        <v>34.7</v>
+      </c>
       <c r="E5">
         <v>19.3</v>
       </c>
+      <c r="F5">
+        <v>27</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>20.1</v>
+      </c>
       <c r="I5">
         <v>34.2</v>
       </c>
+      <c r="J5">
+        <v>29.5</v>
+      </c>
+      <c r="K5">
+        <v>20.1</v>
+      </c>
+      <c r="L5">
+        <v>22.4</v>
+      </c>
       <c r="M5">
         <v>24.4</v>
       </c>
-      <c r="N5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P5" t="s">
-        <v>20</v>
-      </c>
       <c r="R5" s="2">
         <v>25327</v>
       </c>
@@ -692,6 +722,9 @@
       <c r="F6">
         <v>27.6</v>
       </c>
+      <c r="G6">
+        <v>30.9</v>
+      </c>
       <c r="H6">
         <v>21</v>
       </c>
@@ -742,6 +775,9 @@
       <c r="G7">
         <v>0</v>
       </c>
+      <c r="H7">
+        <v>21.2</v>
+      </c>
       <c r="I7">
         <v>29.9</v>
       </c>
@@ -754,6 +790,9 @@
       <c r="L7">
         <v>24</v>
       </c>
+      <c r="M7">
+        <v>24.1</v>
+      </c>
       <c r="R7" s="2">
         <v>25329</v>
       </c>
@@ -775,7 +814,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
       <c r="E8">
         <v>22.6</v>
@@ -799,7 +838,7 @@
         <v>23</v>
       </c>
       <c r="L8">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="M8">
         <v>23.4</v>
@@ -828,7 +867,7 @@
         <v>32.8</v>
       </c>
       <c r="E9">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="F9">
         <v>26.6</v>
@@ -851,6 +890,9 @@
       <c r="L9">
         <v>21.6</v>
       </c>
+      <c r="M9">
+        <v>23.7</v>
+      </c>
       <c r="R9" s="2">
         <v>25331</v>
       </c>
@@ -934,7 +976,7 @@
         <v>25.7</v>
       </c>
       <c r="H11">
-        <v>24</v>
+        <v>21.6</v>
       </c>
       <c r="I11">
         <v>32</v>
@@ -943,7 +985,7 @@
         <v>28.7</v>
       </c>
       <c r="K11">
-        <v>24</v>
+        <v>21.6</v>
       </c>
       <c r="L11">
         <v>23.6</v>
@@ -980,9 +1022,15 @@
       <c r="F12">
         <v>26.7</v>
       </c>
+      <c r="H12">
+        <v>21.2</v>
+      </c>
       <c r="I12">
         <v>32.1</v>
       </c>
+      <c r="J12">
+        <v>28.5</v>
+      </c>
       <c r="K12">
         <v>21.1</v>
       </c>
@@ -990,7 +1038,7 @@
         <v>22.8</v>
       </c>
       <c r="M12">
-        <v>24.4</v>
+        <v>22.9</v>
       </c>
       <c r="R12" s="2">
         <v>25334</v>
@@ -1027,6 +1075,9 @@
       <c r="I13">
         <v>29.9</v>
       </c>
+      <c r="J13">
+        <v>24.3</v>
+      </c>
       <c r="K13">
         <v>22</v>
       </c>
@@ -1034,7 +1085,7 @@
         <v>24.7</v>
       </c>
       <c r="M13">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="R13" s="2">
         <v>25335</v>
@@ -1065,9 +1116,15 @@
       <c r="F14">
         <v>26.5</v>
       </c>
+      <c r="H14">
+        <v>21.6</v>
+      </c>
       <c r="I14">
         <v>30.7</v>
       </c>
+      <c r="J14">
+        <v>27.3</v>
+      </c>
       <c r="K14">
         <v>21.4</v>
       </c>
@@ -1075,7 +1132,7 @@
         <v>22.7</v>
       </c>
       <c r="M14">
-        <v>23.8</v>
+        <v>22.5</v>
       </c>
       <c r="R14" s="2">
         <v>25336</v>
@@ -1112,6 +1169,9 @@
       <c r="I15">
         <v>30.6</v>
       </c>
+      <c r="J15">
+        <v>27.8</v>
+      </c>
       <c r="K15">
         <v>21.5</v>
       </c>
@@ -1119,7 +1179,7 @@
         <v>24.7</v>
       </c>
       <c r="M15">
-        <v>24.6</v>
+        <v>23.5</v>
       </c>
       <c r="R15" s="2">
         <v>25337</v>
@@ -1150,17 +1210,23 @@
       <c r="F16">
         <v>27</v>
       </c>
+      <c r="H16">
+        <v>21.3</v>
+      </c>
       <c r="I16">
         <v>32.4</v>
       </c>
+      <c r="J16">
+        <v>26.5</v>
+      </c>
       <c r="K16">
         <v>21</v>
       </c>
       <c r="L16">
-        <v>25.9</v>
+        <v>23.7</v>
       </c>
       <c r="M16">
-        <v>24.6</v>
+        <v>23.9</v>
       </c>
       <c r="R16" s="2">
         <v>25338</v>
@@ -1197,11 +1263,14 @@
       <c r="H17">
         <v>22.4</v>
       </c>
+      <c r="I17">
+        <v>26.2</v>
+      </c>
       <c r="J17">
         <v>24.4</v>
       </c>
       <c r="L17">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="M17">
         <v>22.2</v>
@@ -1226,11 +1295,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18">
-        <v>26.2</v>
-      </c>
       <c r="E18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18">
         <v>23.1</v>
@@ -1241,6 +1307,9 @@
       <c r="H18">
         <v>21.4</v>
       </c>
+      <c r="I18">
+        <v>24.3</v>
+      </c>
       <c r="J18">
         <v>23.8</v>
       </c>
@@ -1251,7 +1320,10 @@
         <v>23.3</v>
       </c>
       <c r="M18">
-        <v>22.8</v>
+        <v>22.4</v>
+      </c>
+      <c r="N18" t="s">
+        <v>20</v>
       </c>
       <c r="R18" s="2">
         <v>25340</v>
@@ -1274,7 +1346,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="E19">
         <v>20.6</v>
@@ -1288,6 +1360,9 @@
       <c r="H19">
         <v>20.7</v>
       </c>
+      <c r="I19">
+        <v>28.8</v>
+      </c>
       <c r="J19">
         <v>26.9</v>
       </c>
@@ -1298,7 +1373,7 @@
         <v>24.9</v>
       </c>
       <c r="M19">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="R19" s="2">
         <v>25341</v>
@@ -1321,7 +1396,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="E20">
         <v>20.5</v>
@@ -1335,11 +1410,14 @@
       <c r="H20">
         <v>20.9</v>
       </c>
+      <c r="I20">
+        <v>31.2</v>
+      </c>
       <c r="J20">
         <v>28.6</v>
       </c>
       <c r="L20">
-        <v>24.8</v>
+        <v>22.5</v>
       </c>
       <c r="M20">
         <v>23.2</v>
@@ -1377,13 +1455,16 @@
         <v>8.4</v>
       </c>
       <c r="H21">
-        <v>20.1</v>
+        <v>21.1</v>
+      </c>
+      <c r="I21">
+        <v>25.3</v>
       </c>
       <c r="J21">
         <v>22.4</v>
       </c>
       <c r="L21">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="M21">
         <v>21.3</v>
@@ -1421,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="I22">
         <v>31.1</v>
@@ -1430,13 +1511,13 @@
         <v>27.4</v>
       </c>
       <c r="K22">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="L22">
         <v>22.7</v>
       </c>
       <c r="M22">
-        <v>23.8</v>
+        <v>22.5</v>
       </c>
       <c r="R22" s="2">
         <v>25344</v>
@@ -1536,7 +1617,7 @@
         <v>24.2</v>
       </c>
       <c r="M24">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
       <c r="R24" s="2">
         <v>25346</v>
@@ -1583,10 +1664,10 @@
         <v>21.3</v>
       </c>
       <c r="L25">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="M25">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="R25" s="2">
         <v>25347</v>
@@ -1636,7 +1717,7 @@
         <v>23.9</v>
       </c>
       <c r="M26">
-        <v>24.6</v>
+        <v>23.1</v>
       </c>
       <c r="R26" s="2">
         <v>25348</v>
@@ -1677,7 +1758,7 @@
         <v>20.9</v>
       </c>
       <c r="L27">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M27">
         <v>23.2</v>
@@ -1764,6 +1845,9 @@
       <c r="I29">
         <v>22.3</v>
       </c>
+      <c r="J29">
+        <v>24.6</v>
+      </c>
       <c r="K29">
         <v>19.8</v>
       </c>
@@ -1771,7 +1855,7 @@
         <v>21.4</v>
       </c>
       <c r="M29">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="R29" s="2">
         <v>25351</v>
@@ -1856,7 +1940,7 @@
         <v>21.5</v>
       </c>
       <c r="L31">
-        <v>25.5</v>
+        <v>24.3</v>
       </c>
       <c r="M31">
         <v>24.7</v>
@@ -1882,7 +1966,7 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="E32">
         <v>21.3</v>
@@ -1896,6 +1980,9 @@
       <c r="I32">
         <v>32.6</v>
       </c>
+      <c r="J32">
+        <v>28.5</v>
+      </c>
       <c r="K32">
         <v>22.3</v>
       </c>
@@ -1903,7 +1990,7 @@
         <v>24.3</v>
       </c>
       <c r="M32">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
       <c r="R32" s="2">
         <v>25354</v>
@@ -1934,6 +2021,9 @@
       <c r="F33">
         <v>28.1</v>
       </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
       <c r="H33">
         <v>23</v>
       </c>
@@ -1981,6 +2071,9 @@
       <c r="F34">
         <v>25.9</v>
       </c>
+      <c r="G34">
+        <v>1.9</v>
+      </c>
       <c r="H34">
         <v>21.6</v>
       </c>
@@ -1990,8 +2083,11 @@
       <c r="J34">
         <v>22</v>
       </c>
+      <c r="K34">
+        <v>21.4</v>
+      </c>
       <c r="L34">
-        <v>23</v>
+        <v>21.9</v>
       </c>
       <c r="M34">
         <v>21.1</v>
@@ -2025,6 +2121,9 @@
       <c r="F35">
         <v>26.3</v>
       </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
       <c r="H35">
         <v>21.6</v>
       </c>
@@ -2072,6 +2171,9 @@
       <c r="F36">
         <v>26.7</v>
       </c>
+      <c r="G36">
+        <v>0.1</v>
+      </c>
       <c r="H36">
         <v>21.1</v>
       </c>
@@ -2114,11 +2216,14 @@
         <v>33.3</v>
       </c>
       <c r="E37">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F37">
         <v>27.5</v>
       </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
       <c r="H37">
         <v>22.1</v>
       </c>
@@ -2135,7 +2240,7 @@
         <v>22.9</v>
       </c>
       <c r="M37">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="R37" s="2">
         <v>25359</v>
@@ -2161,7 +2266,7 @@
         <v>33.3</v>
       </c>
       <c r="E38">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="F38">
         <v>26.6</v>
@@ -2234,6 +2339,9 @@
       <c r="L39">
         <v>23.4</v>
       </c>
+      <c r="M39">
+        <v>24.3</v>
+      </c>
       <c r="R39" s="2">
         <v>25361</v>
       </c>
@@ -2281,6 +2389,9 @@
       <c r="L40">
         <v>22.5</v>
       </c>
+      <c r="M40">
+        <v>22.8</v>
+      </c>
       <c r="R40" s="2">
         <v>25362</v>
       </c>
@@ -2328,6 +2439,9 @@
       <c r="L41">
         <v>23.1</v>
       </c>
+      <c r="M41">
+        <v>23.3</v>
+      </c>
       <c r="R41" s="2">
         <v>25363</v>
       </c>
@@ -2420,13 +2534,13 @@
         <v>28.3</v>
       </c>
       <c r="K43">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="L43">
         <v>22.8</v>
       </c>
       <c r="M43">
-        <v>25.1</v>
+        <v>24</v>
       </c>
       <c r="R43" s="2">
         <v>25365</v>
@@ -2520,7 +2634,7 @@
         <v>25</v>
       </c>
       <c r="K45">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="L45">
         <v>22.3</v>
@@ -2576,7 +2690,7 @@
         <v>22.3</v>
       </c>
       <c r="M46">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="R46" s="2">
         <v>25368</v>
@@ -2623,10 +2737,10 @@
         <v>19.1</v>
       </c>
       <c r="L47">
-        <v>25.8</v>
+        <v>24</v>
       </c>
       <c r="M47">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="R47" s="2">
         <v>25369</v>
@@ -2660,12 +2774,18 @@
       <c r="G48">
         <v>5.6</v>
       </c>
+      <c r="H48">
+        <v>19.8</v>
+      </c>
       <c r="I48">
         <v>22.9</v>
       </c>
       <c r="J48">
         <v>21.5</v>
       </c>
+      <c r="K48">
+        <v>19.8</v>
+      </c>
       <c r="L48">
         <v>22.1</v>
       </c>
@@ -2704,12 +2824,18 @@
       <c r="G49">
         <v>0</v>
       </c>
+      <c r="H49">
+        <v>20.6</v>
+      </c>
       <c r="I49">
         <v>31.4</v>
       </c>
       <c r="J49">
         <v>27.2</v>
       </c>
+      <c r="K49">
+        <v>20.4</v>
+      </c>
       <c r="L49">
         <v>21.3</v>
       </c>
@@ -2743,7 +2869,7 @@
         <v>19.2</v>
       </c>
       <c r="F50">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2764,7 +2890,7 @@
         <v>22</v>
       </c>
       <c r="M50">
-        <v>25.5</v>
+        <v>24.2</v>
       </c>
       <c r="R50" s="2">
         <v>25372</v>
@@ -2798,17 +2924,23 @@
       <c r="G51">
         <v>0</v>
       </c>
+      <c r="H51">
+        <v>20.1</v>
+      </c>
       <c r="I51">
         <v>29.7</v>
       </c>
       <c r="J51">
         <v>24.4</v>
       </c>
+      <c r="K51">
+        <v>19.9</v>
+      </c>
       <c r="L51">
         <v>23.5</v>
       </c>
       <c r="M51">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="R51" s="2">
         <v>25373</v>
@@ -2858,7 +2990,7 @@
         <v>23.4</v>
       </c>
       <c r="M52">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="R52" s="2">
         <v>25374</v>
@@ -2889,6 +3021,9 @@
       <c r="F53">
         <v>24.7</v>
       </c>
+      <c r="G53">
+        <v>3.4</v>
+      </c>
       <c r="H53">
         <v>21.6</v>
       </c>
@@ -2905,7 +3040,7 @@
         <v>22.9</v>
       </c>
       <c r="M53">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="R53" s="2">
         <v>25375</v>
@@ -2936,6 +3071,9 @@
       <c r="F54">
         <v>22.9</v>
       </c>
+      <c r="G54">
+        <v>4.5</v>
+      </c>
       <c r="H54">
         <v>20.8</v>
       </c>
@@ -2949,7 +3087,7 @@
         <v>20.6</v>
       </c>
       <c r="L54">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="M54">
         <v>22</v>
@@ -2983,6 +3121,9 @@
       <c r="F55">
         <v>24.9</v>
       </c>
+      <c r="G55">
+        <v>5.9</v>
+      </c>
       <c r="H55">
         <v>20.1</v>
       </c>
@@ -3030,8 +3171,11 @@
       <c r="F56">
         <v>24.1</v>
       </c>
+      <c r="G56">
+        <v>2.8</v>
+      </c>
       <c r="H56">
-        <v>11.9</v>
+        <v>18.2</v>
       </c>
       <c r="I56">
         <v>28.3</v>
@@ -3040,13 +3184,13 @@
         <v>26.3</v>
       </c>
       <c r="K56">
-        <v>11.9</v>
+        <v>18.2</v>
       </c>
       <c r="L56">
-        <v>24.8</v>
+        <v>23.5</v>
       </c>
       <c r="M56">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="R56" s="2">
         <v>25378</v>
@@ -3077,6 +3221,9 @@
       <c r="F57">
         <v>24.9</v>
       </c>
+      <c r="G57">
+        <v>1.3</v>
+      </c>
       <c r="H57">
         <v>21.9</v>
       </c>
@@ -3093,7 +3240,7 @@
         <v>20.6</v>
       </c>
       <c r="M57">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="R57" s="2">
         <v>25379</v>
@@ -3137,7 +3284,7 @@
         <v>19.5</v>
       </c>
       <c r="L58">
-        <v>25.5</v>
+        <v>23.7</v>
       </c>
       <c r="M58">
         <v>23.9</v>
@@ -3166,7 +3313,7 @@
         <v>30.8</v>
       </c>
       <c r="E59">
-        <v>20.06</v>
+        <v>20.6</v>
       </c>
       <c r="F59">
         <v>25.7</v>
@@ -3181,10 +3328,10 @@
         <v>28</v>
       </c>
       <c r="K59">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L59">
-        <v>25.3</v>
+        <v>23.4</v>
       </c>
       <c r="M59">
         <v>24</v>
@@ -3231,10 +3378,10 @@
         <v>19.9</v>
       </c>
       <c r="L60">
-        <v>24.9</v>
+        <v>23.4</v>
       </c>
       <c r="M60">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
       <c r="R60" s="2">
         <v>25382</v>
@@ -3281,7 +3428,7 @@
         <v>22.7</v>
       </c>
       <c r="M61">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="R61" s="2">
         <v>25383</v>

--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
@@ -814,7 +814,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="E8">
         <v>22.6</v>
@@ -1022,9 +1022,6 @@
       <c r="F12">
         <v>26.7</v>
       </c>
-      <c r="H12">
-        <v>21.2</v>
-      </c>
       <c r="I12">
         <v>32.1</v>
       </c>
@@ -1210,9 +1207,6 @@
       <c r="F16">
         <v>27</v>
       </c>
-      <c r="H16">
-        <v>21.3</v>
-      </c>
       <c r="I16">
         <v>32.4</v>
       </c>
@@ -1416,6 +1410,9 @@
       <c r="J20">
         <v>28.6</v>
       </c>
+      <c r="K20">
+        <v>20.6</v>
+      </c>
       <c r="L20">
         <v>22.5</v>
       </c>
@@ -1567,7 +1564,7 @@
         <v>23.1</v>
       </c>
       <c r="M23">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="R23" s="2">
         <v>25345</v>
@@ -1667,7 +1664,7 @@
         <v>22.7</v>
       </c>
       <c r="M25">
-        <v>24.6</v>
+        <v>23.5</v>
       </c>
       <c r="R25" s="2">
         <v>25347</v>
@@ -1743,7 +1740,7 @@
         <v>31.9</v>
       </c>
       <c r="E27">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F27">
         <v>26.1</v>
@@ -1754,6 +1751,9 @@
       <c r="I27">
         <v>31.9</v>
       </c>
+      <c r="J27">
+        <v>24.7</v>
+      </c>
       <c r="K27">
         <v>20.9</v>
       </c>
@@ -1892,6 +1892,9 @@
       <c r="I30">
         <v>24.1</v>
       </c>
+      <c r="J30">
+        <v>24.7</v>
+      </c>
       <c r="K30">
         <v>21.8</v>
       </c>
@@ -1936,6 +1939,9 @@
       <c r="I31">
         <v>29.1</v>
       </c>
+      <c r="J31">
+        <v>27.8</v>
+      </c>
       <c r="K31">
         <v>21.5</v>
       </c>
@@ -2666,7 +2672,7 @@
         <v>30.1</v>
       </c>
       <c r="E46">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="F46">
         <v>24.1</v>
@@ -3175,7 +3181,7 @@
         <v>2.8</v>
       </c>
       <c r="H56">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="I56">
         <v>28.3</v>
@@ -3184,7 +3190,7 @@
         <v>26.3</v>
       </c>
       <c r="K56">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="L56">
         <v>23.5</v>
@@ -3328,7 +3334,7 @@
         <v>28</v>
       </c>
       <c r="K59">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="L59">
         <v>23.4</v>

--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
@@ -1022,6 +1022,9 @@
       <c r="F12">
         <v>26.7</v>
       </c>
+      <c r="H12">
+        <v>21.2</v>
+      </c>
       <c r="I12">
         <v>32.1</v>
       </c>
@@ -1207,6 +1210,9 @@
       <c r="F16">
         <v>27</v>
       </c>
+      <c r="H16">
+        <v>21.3</v>
+      </c>
       <c r="I16">
         <v>32.4</v>
       </c>
@@ -1564,7 +1570,7 @@
         <v>23.1</v>
       </c>
       <c r="M23">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="R23" s="2">
         <v>25345</v>
@@ -1740,7 +1746,7 @@
         <v>31.9</v>
       </c>
       <c r="E27">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F27">
         <v>26.1</v>
@@ -1808,7 +1814,7 @@
         <v>23.7</v>
       </c>
       <c r="M28">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="R28" s="2">
         <v>25350</v>
@@ -2272,7 +2278,7 @@
         <v>33.3</v>
       </c>
       <c r="E38">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="F38">
         <v>26.6</v>
@@ -2672,7 +2678,7 @@
         <v>30.1</v>
       </c>
       <c r="E46">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="F46">
         <v>24.1</v>
@@ -3181,7 +3187,7 @@
         <v>2.8</v>
       </c>
       <c r="H56">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="I56">
         <v>28.3</v>
@@ -3190,7 +3196,7 @@
         <v>26.3</v>
       </c>
       <c r="K56">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="L56">
         <v>23.5</v>
@@ -3246,7 +3252,7 @@
         <v>20.6</v>
       </c>
       <c r="M57">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="R57" s="2">
         <v>25379</v>

--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_temperature_and_precipitation_station_203.xlsx
@@ -538,10 +538,10 @@
         <v>20.1</v>
       </c>
       <c r="L2">
-        <v>22.4</v>
+        <v>24.1</v>
       </c>
       <c r="M2">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="R2" s="2">
         <v>25324</v>
@@ -588,7 +588,7 @@
         <v>18.8</v>
       </c>
       <c r="L3">
-        <v>22.8</v>
+        <v>25.4</v>
       </c>
       <c r="M3">
         <v>24</v>
@@ -641,7 +641,7 @@
         <v>25.7</v>
       </c>
       <c r="M4">
-        <v>21.8</v>
+        <v>23.7</v>
       </c>
       <c r="R4" s="2">
         <v>25326</v>
@@ -688,7 +688,7 @@
         <v>20.1</v>
       </c>
       <c r="L5">
-        <v>22.4</v>
+        <v>25.5</v>
       </c>
       <c r="M5">
         <v>24.4</v>
@@ -788,10 +788,10 @@
         <v>20.9</v>
       </c>
       <c r="L7">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="M7">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="R7" s="2">
         <v>25329</v>
@@ -838,10 +838,10 @@
         <v>23</v>
       </c>
       <c r="L8">
-        <v>22.4</v>
+        <v>24.9</v>
       </c>
       <c r="M8">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
       <c r="R8" s="2">
         <v>25330</v>
@@ -888,10 +888,10 @@
         <v>21.9</v>
       </c>
       <c r="L9">
-        <v>21.6</v>
+        <v>24.6</v>
       </c>
       <c r="M9">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
       <c r="R9" s="2">
         <v>25331</v>
@@ -988,10 +988,10 @@
         <v>21.6</v>
       </c>
       <c r="L11">
-        <v>23.6</v>
+        <v>25.8</v>
       </c>
       <c r="M11">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="R11" s="2">
         <v>25333</v>
@@ -1035,10 +1035,10 @@
         <v>21.1</v>
       </c>
       <c r="L12">
-        <v>22.8</v>
+        <v>25.2</v>
       </c>
       <c r="M12">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="R12" s="2">
         <v>25334</v>
@@ -1082,10 +1082,10 @@
         <v>22</v>
       </c>
       <c r="L13">
-        <v>24.7</v>
+        <v>26</v>
       </c>
       <c r="M13">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="R13" s="2">
         <v>25335</v>
@@ -1129,10 +1129,10 @@
         <v>21.4</v>
       </c>
       <c r="L14">
-        <v>22.7</v>
+        <v>24.8</v>
       </c>
       <c r="M14">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="R14" s="2">
         <v>25336</v>
@@ -1176,10 +1176,10 @@
         <v>21.5</v>
       </c>
       <c r="L15">
-        <v>24.7</v>
+        <v>26.2</v>
       </c>
       <c r="M15">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="R15" s="2">
         <v>25337</v>
@@ -1223,10 +1223,10 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>23.7</v>
+        <v>25.9</v>
       </c>
       <c r="M16">
-        <v>23.9</v>
+        <v>24.6</v>
       </c>
       <c r="R16" s="2">
         <v>25338</v>
@@ -1269,11 +1269,14 @@
       <c r="J17">
         <v>24.4</v>
       </c>
+      <c r="K17">
+        <v>21.9</v>
+      </c>
       <c r="L17">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="M17">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="R17" s="2">
         <v>25339</v>
@@ -1320,7 +1323,7 @@
         <v>23.3</v>
       </c>
       <c r="M18">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="N18" t="s">
         <v>20</v>
@@ -1373,7 +1376,7 @@
         <v>24.9</v>
       </c>
       <c r="M19">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="R19" s="2">
         <v>25341</v>
@@ -1420,10 +1423,10 @@
         <v>20.6</v>
       </c>
       <c r="L20">
-        <v>22.5</v>
+        <v>24.8</v>
       </c>
       <c r="M20">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
       <c r="R20" s="2">
         <v>25342</v>
@@ -1466,8 +1469,11 @@
       <c r="J21">
         <v>22.4</v>
       </c>
+      <c r="K21">
+        <v>20.6</v>
+      </c>
       <c r="L21">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="M21">
         <v>21.3</v>
@@ -1517,10 +1523,10 @@
         <v>20.1</v>
       </c>
       <c r="L22">
-        <v>22.7</v>
+        <v>24.9</v>
       </c>
       <c r="M22">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="R22" s="2">
         <v>25344</v>
@@ -1567,7 +1573,7 @@
         <v>21.4</v>
       </c>
       <c r="L23">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="M23">
         <v>23.8</v>
@@ -1617,10 +1623,10 @@
         <v>21.7</v>
       </c>
       <c r="L24">
-        <v>24.2</v>
+        <v>25.8</v>
       </c>
       <c r="M24">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="R24" s="2">
         <v>25346</v>
@@ -1667,10 +1673,10 @@
         <v>21.3</v>
       </c>
       <c r="L25">
-        <v>22.7</v>
+        <v>24.9</v>
       </c>
       <c r="M25">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="R25" s="2">
         <v>25347</v>
@@ -1717,10 +1723,10 @@
         <v>20.7</v>
       </c>
       <c r="L26">
-        <v>23.9</v>
+        <v>26</v>
       </c>
       <c r="M26">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="R26" s="2">
         <v>25348</v>
@@ -1764,7 +1770,7 @@
         <v>20.9</v>
       </c>
       <c r="L27">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M27">
         <v>23.2</v>
@@ -1811,7 +1817,7 @@
         <v>19.6</v>
       </c>
       <c r="L28">
-        <v>23.7</v>
+        <v>26</v>
       </c>
       <c r="M28">
         <v>23.8</v>
@@ -1861,7 +1867,7 @@
         <v>21.4</v>
       </c>
       <c r="M29">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="R29" s="2">
         <v>25351</v>
@@ -1952,7 +1958,7 @@
         <v>21.5</v>
       </c>
       <c r="L31">
-        <v>24.3</v>
+        <v>25.5</v>
       </c>
       <c r="M31">
         <v>24.7</v>
@@ -1999,10 +2005,10 @@
         <v>22.3</v>
       </c>
       <c r="L32">
-        <v>24.3</v>
+        <v>26.4</v>
       </c>
       <c r="M32">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="R32" s="2">
         <v>25354</v>
@@ -2049,10 +2055,10 @@
         <v>22.7</v>
       </c>
       <c r="L33">
-        <v>23</v>
+        <v>25.6</v>
       </c>
       <c r="M33">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
       <c r="R33" s="2">
         <v>25355</v>
@@ -2099,7 +2105,7 @@
         <v>21.4</v>
       </c>
       <c r="L34">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="M34">
         <v>21.1</v>
@@ -2149,10 +2155,10 @@
         <v>21.3</v>
       </c>
       <c r="L35">
-        <v>22.5</v>
+        <v>24.9</v>
       </c>
       <c r="M35">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="R35" s="2">
         <v>25357</v>
@@ -2199,10 +2205,10 @@
         <v>20.9</v>
       </c>
       <c r="L36">
-        <v>22.9</v>
+        <v>25.3</v>
       </c>
       <c r="M36">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="R36" s="2">
         <v>25358</v>
@@ -2249,10 +2255,10 @@
         <v>21.7</v>
       </c>
       <c r="L37">
-        <v>22.9</v>
+        <v>25.6</v>
       </c>
       <c r="M37">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="R37" s="2">
         <v>25359</v>
@@ -2299,10 +2305,10 @@
         <v>20.5</v>
       </c>
       <c r="L38">
-        <v>23.2</v>
+        <v>25.8</v>
       </c>
       <c r="M38">
-        <v>23.5</v>
+        <v>25.1</v>
       </c>
       <c r="R38" s="2">
         <v>25360</v>
@@ -2349,10 +2355,10 @@
         <v>20.1</v>
       </c>
       <c r="L39">
-        <v>23.4</v>
+        <v>25.8</v>
       </c>
       <c r="M39">
-        <v>24.3</v>
+        <v>25.6</v>
       </c>
       <c r="R39" s="2">
         <v>25361</v>
@@ -2399,10 +2405,10 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="M40">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="R40" s="2">
         <v>25362</v>
@@ -2449,10 +2455,10 @@
         <v>20.9</v>
       </c>
       <c r="L41">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="M41">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="R41" s="2">
         <v>25363</v>
@@ -2499,10 +2505,10 @@
         <v>19.4</v>
       </c>
       <c r="L42">
-        <v>24.1</v>
+        <v>25.6</v>
       </c>
       <c r="M42">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="R42" s="2">
         <v>25364</v>
@@ -2549,10 +2555,10 @@
         <v>19.4</v>
       </c>
       <c r="L43">
-        <v>22.8</v>
+        <v>25.3</v>
       </c>
       <c r="M43">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="R43" s="2">
         <v>25365</v>
@@ -2599,10 +2605,10 @@
         <v>20.7</v>
       </c>
       <c r="L44">
-        <v>23.1</v>
+        <v>25.3</v>
       </c>
       <c r="M44">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="R44" s="2">
         <v>25366</v>
@@ -2649,10 +2655,10 @@
         <v>19.7</v>
       </c>
       <c r="L45">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="M45">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="R45" s="2">
         <v>25367</v>
@@ -2699,10 +2705,10 @@
         <v>18.9</v>
       </c>
       <c r="L46">
-        <v>22.3</v>
+        <v>24.4</v>
       </c>
       <c r="M46">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="R46" s="2">
         <v>25368</v>
@@ -2749,10 +2755,10 @@
         <v>19.1</v>
       </c>
       <c r="L47">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="M47">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="R47" s="2">
         <v>25369</v>
@@ -2849,10 +2855,10 @@
         <v>20.4</v>
       </c>
       <c r="L49">
-        <v>21.3</v>
+        <v>24.1</v>
       </c>
       <c r="M49">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="R49" s="2">
         <v>25371</v>
@@ -2899,10 +2905,10 @@
         <v>19.5</v>
       </c>
       <c r="L50">
-        <v>22</v>
+        <v>24.9</v>
       </c>
       <c r="M50">
-        <v>24.2</v>
+        <v>25.5</v>
       </c>
       <c r="R50" s="2">
         <v>25372</v>
@@ -2949,10 +2955,10 @@
         <v>19.9</v>
       </c>
       <c r="L51">
-        <v>23.5</v>
+        <v>25.1</v>
       </c>
       <c r="M51">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
       <c r="R51" s="2">
         <v>25373</v>
@@ -2999,10 +3005,10 @@
         <v>21.5</v>
       </c>
       <c r="L52">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="M52">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="R52" s="2">
         <v>25374</v>
@@ -3049,10 +3055,10 @@
         <v>21.5</v>
       </c>
       <c r="L53">
-        <v>22.9</v>
+        <v>24.5</v>
       </c>
       <c r="M53">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="R53" s="2">
         <v>25375</v>
@@ -3099,7 +3105,7 @@
         <v>20.6</v>
       </c>
       <c r="L54">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
       <c r="M54">
         <v>22</v>
@@ -3149,10 +3155,10 @@
         <v>20.1</v>
       </c>
       <c r="L55">
-        <v>24</v>
+        <v>25.6</v>
       </c>
       <c r="M55">
-        <v>18.6</v>
+        <v>21</v>
       </c>
       <c r="R55" s="2">
         <v>25377</v>
@@ -3196,13 +3202,13 @@
         <v>26.3</v>
       </c>
       <c r="K56">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="L56">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="M56">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="R56" s="2">
         <v>25378</v>
@@ -3249,7 +3255,7 @@
         <v>21.7</v>
       </c>
       <c r="L57">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="M57">
         <v>20.8</v>
@@ -3293,10 +3299,10 @@
         <v>27.8</v>
       </c>
       <c r="K58">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="L58">
-        <v>23.7</v>
+        <v>25.5</v>
       </c>
       <c r="M58">
         <v>23.9</v>
@@ -3343,7 +3349,7 @@
         <v>20.9</v>
       </c>
       <c r="L59">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="M59">
         <v>24</v>
@@ -3387,13 +3393,13 @@
         <v>27.1</v>
       </c>
       <c r="K60">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="L60">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
       <c r="M60">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="R60" s="2">
         <v>25382</v>
@@ -3437,10 +3443,10 @@
         <v>21.2</v>
       </c>
       <c r="L61">
-        <v>22.7</v>
+        <v>24.9</v>
       </c>
       <c r="M61">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="R61" s="2">
         <v>25383</v>
@@ -3484,7 +3490,7 @@
         <v>21.1</v>
       </c>
       <c r="L62">
-        <v>20.4</v>
+        <v>21.7</v>
       </c>
       <c r="M62">
         <v>22</v>
